--- a/survey_templates/050_urban_public_spaces_governance_quiz--survey_templates.xlsx
+++ b/survey_templates/050_urban_public_spaces_governance_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>public_space_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>Public Space Management</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your thoughts on public space management</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -553,7 +557,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Please provide your thoughts on public space participation</t>
+          <t>Public Space Participation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -578,7 +582,11 @@
           <t>Governance Priorities</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide your priorities for governance</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -643,17 +651,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>public_space_maintenance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Public Space Management</t>
+          <t>Public Space Maintenance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Please provide your thoughts on public space management</t>
+          <t>Please provide your thoughts on public space maintenance</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -670,12 +678,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_input_7</t>
+          <t>public_space_safety</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Public Space Maintenance</t>
+          <t>Public Space Safety</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -693,19 +701,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_input_8</t>
+          <t>public_space_accessibility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Public Space Safety</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Please provide your thoughts on public space safety</t>
-        </is>
-      </c>
+          <t>Public Space Accessibility</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -720,15 +724,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_input_9</t>
+          <t>public_space_usage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Public Space Accessibility</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Public Space Usage</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide your thoughts on public space usage</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -743,19 +751,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_input_10</t>
+          <t>public_space_governance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Public Space Usage</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Please provide your thoughts on public space usage</t>
-        </is>
-      </c>
+          <t>Public Space Governance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -770,17 +774,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>public_space_governance</t>
+          <t>user_input_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Public Space Governance</t>
+          <t>User Input 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Please describe the governance of public space</t>
+          <t>Please describe the maintenance of public space</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -797,19 +801,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input_12</t>
+          <t>urban_planning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Public Space Maintenance</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Please describe the maintenance of public space</t>
-        </is>
-      </c>
+          <t>Urban Planning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,333 +819,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>public_space_safety</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Public Space Safety</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Please describe the safety of public space</t>
-        </is>
-      </c>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>public_space_maintenance</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Public Space Maintenance</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Describe the maintenance of public space</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>urban_planning</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Urban Planning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>user_input_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>User input 15</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>public_space_participation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Public Space Participation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Public Space Participation</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>user_input_16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>User input 16</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>User input 16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>public_space_governance</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Public Space Governance</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Public Space Governance</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>user_input_17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>User input 17</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>User input 17</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>public_space_safety</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Public Space Safety</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Public Space Safety</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_input_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>User input 18</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>User input 18</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>public_space_maintenance</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Public Space Maintenance</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Public Space Maintenance</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>user_input_19</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>User input 19</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1166,8 +854,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1195,12 +883,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1212,12 +900,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1229,12 +917,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
